--- a/dutch-words.xlsx
+++ b/dutch-words.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pedro/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pedro/Desktop/my-projects/dutch-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CD2D89-6B30-E14D-97E4-E8A0123111F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E266A14F-CA76-8B40-AA45-2308935737D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34560" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="1938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="1937">
   <si>
     <t>Dutch</t>
   </si>
@@ -2147,9 +2147,6 @@
   </si>
   <si>
     <t>(I) go</t>
-  </si>
-  <si>
-    <t>t</t>
   </si>
   <si>
     <t>bent</t>
@@ -5852,11 +5849,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -6368,7 +6367,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>709</v>
+        <v>38</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -6376,10 +6375,10 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -6387,7 +6386,7 @@
         <v>494</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -6395,23 +6394,23 @@
         <v>173</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>716</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -6419,7 +6418,7 @@
         <v>449</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -6427,7 +6426,7 @@
         <v>203</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -6435,7 +6434,7 @@
         <v>213</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -6443,7 +6442,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -6467,7 +6466,7 @@
         <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -6499,7 +6498,7 @@
         <v>186</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -6515,7 +6514,7 @@
         <v>259</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -6523,7 +6522,7 @@
         <v>483</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -6539,15 +6538,15 @@
         <v>185</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -6555,7 +6554,7 @@
         <v>122</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -6563,15 +6562,15 @@
         <v>578</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>731</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
@@ -6587,7 +6586,7 @@
         <v>25</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
@@ -6603,7 +6602,7 @@
         <v>291</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
@@ -6611,23 +6610,23 @@
         <v>256</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>738</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
@@ -6643,7 +6642,7 @@
         <v>181</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
@@ -6651,7 +6650,7 @@
         <v>73</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
@@ -6707,7 +6706,7 @@
         <v>189</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
@@ -6715,7 +6714,7 @@
         <v>267</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -6723,7 +6722,7 @@
         <v>210</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
@@ -6752,10 +6751,10 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>745</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -6763,7 +6762,7 @@
         <v>179</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
@@ -6771,7 +6770,7 @@
         <v>419</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
@@ -6779,7 +6778,7 @@
         <v>24</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
@@ -6787,7 +6786,7 @@
         <v>29</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
@@ -6803,15 +6802,15 @@
         <v>157</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>752</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
@@ -6824,10 +6823,10 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>754</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
@@ -6843,15 +6842,15 @@
         <v>292</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -6867,7 +6866,7 @@
         <v>501</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
@@ -6875,7 +6874,7 @@
         <v>482</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
@@ -6883,7 +6882,7 @@
         <v>500</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
@@ -6891,7 +6890,7 @@
         <v>175</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
@@ -6899,15 +6898,15 @@
         <v>456</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>764</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
@@ -6923,7 +6922,7 @@
         <v>431</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
@@ -6931,15 +6930,15 @@
         <v>529</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>768</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -6947,7 +6946,7 @@
         <v>269</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
@@ -6963,7 +6962,7 @@
         <v>268</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
@@ -6971,7 +6970,7 @@
         <v>421</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
@@ -6987,7 +6986,7 @@
         <v>297</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -6995,15 +6994,15 @@
         <v>85</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
@@ -7011,7 +7010,7 @@
         <v>89</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
@@ -7024,7 +7023,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>471</v>
@@ -7043,15 +7042,15 @@
         <v>3</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -7059,7 +7058,7 @@
         <v>649</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
@@ -7072,10 +7071,10 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>783</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
@@ -7083,15 +7082,15 @@
         <v>158</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>786</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
@@ -7104,10 +7103,10 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>788</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
@@ -7123,7 +7122,7 @@
         <v>199</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
@@ -7131,23 +7130,23 @@
         <v>197</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>792</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
@@ -7171,15 +7170,15 @@
         <v>385</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
@@ -7192,10 +7191,10 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>799</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
@@ -7203,7 +7202,7 @@
         <v>515</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
@@ -7219,7 +7218,7 @@
         <v>618</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
@@ -7227,7 +7226,7 @@
         <v>508</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
@@ -7240,10 +7239,10 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>804</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -7251,23 +7250,23 @@
         <v>9</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="B135" s="3" t="s">
         <v>807</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
@@ -7275,7 +7274,7 @@
         <v>398</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
@@ -7291,7 +7290,7 @@
         <v>253</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
@@ -7299,7 +7298,7 @@
         <v>446</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
@@ -7315,15 +7314,15 @@
         <v>285</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="B143" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
@@ -7339,7 +7338,7 @@
         <v>2</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
@@ -7347,23 +7346,23 @@
         <v>447</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="B147" s="3" t="s">
         <v>819</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>821</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
@@ -7371,7 +7370,7 @@
         <v>67</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
@@ -7379,7 +7378,7 @@
         <v>496</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
@@ -7392,10 +7391,10 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>825</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
@@ -7403,15 +7402,15 @@
         <v>156</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="B154" s="3" t="s">
         <v>828</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
@@ -7419,7 +7418,7 @@
         <v>163</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
@@ -7432,18 +7431,18 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>831</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="B158" s="3" t="s">
         <v>833</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
@@ -7464,26 +7463,26 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>835</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="B162" s="3" t="s">
         <v>837</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>839</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
@@ -7491,7 +7490,7 @@
         <v>357</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
@@ -7504,26 +7503,26 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="B166" s="3" t="s">
         <v>842</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B167" s="2" t="s">
         <v>844</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="B168" s="3" t="s">
         <v>846</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
@@ -7539,7 +7538,7 @@
         <v>555</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
@@ -7547,7 +7546,7 @@
         <v>685</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
@@ -7563,7 +7562,7 @@
         <v>360</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
@@ -7584,18 +7583,18 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="B176" s="3" t="s">
         <v>851</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="B177" s="3" t="s">
         <v>853</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
@@ -7603,15 +7602,15 @@
         <v>461</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="B179" s="3" t="s">
         <v>856</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
@@ -7619,23 +7618,23 @@
         <v>282</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="B181" s="3" t="s">
         <v>859</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>861</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
@@ -7648,10 +7647,10 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="B184" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
@@ -7659,7 +7658,7 @@
         <v>299</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
@@ -7667,39 +7666,39 @@
         <v>343</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="B187" s="3" t="s">
         <v>867</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B188" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="B189" s="3" t="s">
         <v>871</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B190" s="2" t="s">
         <v>873</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
@@ -7707,7 +7706,7 @@
         <v>286</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
@@ -7728,10 +7727,10 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B194" s="2" t="s">
         <v>876</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
@@ -7739,15 +7738,15 @@
         <v>294</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>879</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
@@ -7755,31 +7754,31 @@
         <v>155</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>882</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="B199" s="3" t="s">
         <v>884</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B200" s="2" t="s">
         <v>886</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
@@ -7795,23 +7794,23 @@
         <v>51</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B203" s="2" t="s">
         <v>889</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="B204" s="3" t="s">
         <v>891</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
@@ -7819,7 +7818,7 @@
         <v>67</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
@@ -7827,15 +7826,15 @@
         <v>116</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B207" s="2" t="s">
         <v>895</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
@@ -7843,7 +7842,7 @@
         <v>592</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -7856,18 +7855,18 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="B210" s="3" t="s">
         <v>898</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="B211" s="2" t="s">
         <v>900</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
@@ -7875,7 +7874,7 @@
         <v>345</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -7883,7 +7882,7 @@
         <v>502</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
@@ -7891,15 +7890,15 @@
         <v>579</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>905</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -7907,7 +7906,7 @@
         <v>364</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
@@ -7915,7 +7914,7 @@
         <v>518</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
@@ -7923,7 +7922,7 @@
         <v>440</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
@@ -7931,7 +7930,7 @@
         <v>375</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -7939,7 +7938,7 @@
         <v>95</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -7968,10 +7967,10 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="B224" s="3" t="s">
         <v>912</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
@@ -7979,15 +7978,15 @@
         <v>550</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="B226" s="3" t="s">
         <v>915</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
@@ -7995,23 +7994,23 @@
         <v>495</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>918</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="B229" s="3" t="s">
         <v>920</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
@@ -8027,31 +8026,31 @@
         <v>445</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>923</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="B233" s="3" t="s">
         <v>925</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="B234" s="2" t="s">
         <v>927</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
@@ -8064,10 +8063,10 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="B236" s="2" t="s">
         <v>929</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
@@ -8075,15 +8074,15 @@
         <v>679</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B238" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
@@ -8096,10 +8095,10 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>934</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
@@ -8115,15 +8114,15 @@
         <v>198</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="B243" s="3" t="s">
         <v>937</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
@@ -8131,15 +8130,15 @@
         <v>575</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="B245" s="3" t="s">
         <v>940</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
@@ -8160,26 +8159,26 @@
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B248" s="2" t="s">
         <v>942</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="B249" s="3" t="s">
         <v>944</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="B250" s="2" t="s">
         <v>946</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -8187,7 +8186,7 @@
         <v>97</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
@@ -8211,15 +8210,15 @@
         <v>296</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="B255" s="2" t="s">
         <v>950</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
@@ -8235,39 +8234,39 @@
         <v>223</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="B258" s="3" t="s">
         <v>953</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="B260" s="3" t="s">
         <v>956</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B261" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
@@ -8275,12 +8274,12 @@
         <v>152</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>558</v>
@@ -8288,10 +8287,10 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="B264" s="3" t="s">
         <v>962</v>
-      </c>
-      <c r="B264" s="3" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
@@ -8299,15 +8298,15 @@
         <v>594</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B266" s="3" t="s">
         <v>965</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
@@ -8315,7 +8314,7 @@
         <v>569</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
@@ -8328,10 +8327,10 @@
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>968</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
@@ -8339,7 +8338,7 @@
         <v>35</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
@@ -8347,7 +8346,7 @@
         <v>34</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
@@ -8355,39 +8354,39 @@
         <v>32</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="B273" s="2" t="s">
         <v>973</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="B274" s="3" t="s">
         <v>975</v>
-      </c>
-      <c r="B274" s="3" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>977</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="B276" s="3" t="s">
         <v>979</v>
-      </c>
-      <c r="B276" s="3" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
@@ -8395,7 +8394,7 @@
         <v>525</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
@@ -8408,42 +8407,42 @@
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="B279" s="3" t="s">
         <v>982</v>
-      </c>
-      <c r="B279" s="3" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>984</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="B281" s="3" t="s">
         <v>986</v>
-      </c>
-      <c r="B281" s="3" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="B282" s="2" t="s">
         <v>988</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="B283" s="3" t="s">
         <v>990</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
@@ -8456,10 +8455,10 @@
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
@@ -8483,15 +8482,15 @@
         <v>557</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="B289" s="3" t="s">
         <v>994</v>
-      </c>
-      <c r="B289" s="3" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
@@ -8507,7 +8506,7 @@
         <v>121</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
@@ -8523,7 +8522,7 @@
         <v>346</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
@@ -8531,7 +8530,7 @@
         <v>289</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
@@ -8539,7 +8538,7 @@
         <v>342</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
@@ -8552,18 +8551,18 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="B297" s="3" t="s">
         <v>1000</v>
-      </c>
-      <c r="B297" s="3" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>1002</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
@@ -8571,12 +8570,12 @@
         <v>581</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>604</v>
@@ -8592,10 +8591,10 @@
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B302" s="3" t="s">
         <v>1006</v>
-      </c>
-      <c r="B302" s="3" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
@@ -8611,23 +8610,23 @@
         <v>14</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B305" s="2" t="s">
         <v>1009</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B306" s="3" t="s">
         <v>1011</v>
-      </c>
-      <c r="B306" s="3" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
@@ -8635,7 +8634,7 @@
         <v>617</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
@@ -8643,47 +8642,47 @@
         <v>661</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B309" s="2" t="s">
         <v>1015</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B310" s="3" t="s">
         <v>1017</v>
-      </c>
-      <c r="B310" s="3" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B312" s="3" t="s">
         <v>1020</v>
-      </c>
-      <c r="B312" s="3" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>1022</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
@@ -8696,10 +8695,10 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>1024</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
@@ -8712,23 +8711,23 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B317" s="2" t="s">
         <v>1026</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B318" s="3" t="s">
         <v>1028</v>
-      </c>
-      <c r="B318" s="3" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>562</v>
@@ -8736,18 +8735,18 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B320" s="3" t="s">
         <v>1031</v>
-      </c>
-      <c r="B320" s="3" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>1033</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
@@ -8755,7 +8754,7 @@
         <v>514</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
@@ -8763,15 +8762,15 @@
         <v>681</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B324" s="3" t="s">
         <v>1037</v>
-      </c>
-      <c r="B324" s="3" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
@@ -8792,42 +8791,42 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B327" s="3" t="s">
         <v>1039</v>
-      </c>
-      <c r="B327" s="3" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B328" s="2" t="s">
         <v>1041</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B329" s="3" t="s">
         <v>1043</v>
-      </c>
-      <c r="B329" s="3" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B330" s="2" t="s">
         <v>1045</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B331" s="3" t="s">
         <v>1047</v>
-      </c>
-      <c r="B331" s="3" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
@@ -8835,7 +8834,7 @@
         <v>409</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
@@ -8843,7 +8842,7 @@
         <v>548</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
@@ -8856,23 +8855,23 @@
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B335" s="3" t="s">
         <v>1051</v>
-      </c>
-      <c r="B335" s="3" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B336" s="2" t="s">
         <v>1053</v>
-      </c>
-      <c r="B336" s="2" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>560</v>
@@ -8880,10 +8879,10 @@
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B338" s="2" t="s">
         <v>1056</v>
-      </c>
-      <c r="B338" s="2" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
@@ -8899,7 +8898,7 @@
         <v>324</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
@@ -8907,7 +8906,7 @@
         <v>577</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
@@ -8915,7 +8914,7 @@
         <v>221</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
@@ -8923,15 +8922,15 @@
         <v>476</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B344" s="2" t="s">
         <v>1062</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
@@ -8955,12 +8954,12 @@
         <v>404</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>564</v>
@@ -8971,15 +8970,15 @@
         <v>642</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B350" s="2" t="s">
         <v>1067</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
@@ -8987,7 +8986,7 @@
         <v>80</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
@@ -8995,7 +8994,7 @@
         <v>311</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
@@ -9003,7 +9002,7 @@
         <v>400</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
@@ -9011,7 +9010,7 @@
         <v>365</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
@@ -9019,15 +9018,15 @@
         <v>300</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B356" s="3" t="s">
         <v>1074</v>
-      </c>
-      <c r="B356" s="3" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
@@ -9048,50 +9047,50 @@
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B359" s="2" t="s">
         <v>1076</v>
-      </c>
-      <c r="B359" s="2" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B360" s="3" t="s">
         <v>1078</v>
-      </c>
-      <c r="B360" s="3" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B361" s="2" t="s">
         <v>1080</v>
-      </c>
-      <c r="B361" s="2" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B362" s="3" t="s">
         <v>1082</v>
-      </c>
-      <c r="B362" s="3" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B363" s="2" t="s">
         <v>1084</v>
-      </c>
-      <c r="B363" s="2" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B364" s="3" t="s">
         <v>1086</v>
-      </c>
-      <c r="B364" s="3" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
@@ -9107,23 +9106,23 @@
         <v>288</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B367" s="2" t="s">
         <v>1089</v>
-      </c>
-      <c r="B367" s="2" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B368" s="3" t="s">
         <v>1091</v>
-      </c>
-      <c r="B368" s="3" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
@@ -9131,7 +9130,7 @@
         <v>180</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
@@ -9147,7 +9146,7 @@
         <v>304</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
@@ -9155,15 +9154,15 @@
         <v>653</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B373" s="2" t="s">
         <v>1096</v>
-      </c>
-      <c r="B373" s="2" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
@@ -9171,7 +9170,7 @@
         <v>355</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
@@ -9179,23 +9178,23 @@
         <v>363</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B376" s="3" t="s">
         <v>1100</v>
-      </c>
-      <c r="B376" s="3" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B377" s="3" t="s">
         <v>1102</v>
-      </c>
-      <c r="B377" s="3" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
@@ -9211,7 +9210,7 @@
         <v>472</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
@@ -9219,15 +9218,15 @@
         <v>574</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B381" s="3" t="s">
         <v>1106</v>
-      </c>
-      <c r="B381" s="3" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
@@ -9243,7 +9242,7 @@
         <v>341</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
@@ -9251,7 +9250,7 @@
         <v>318</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
@@ -9259,7 +9258,7 @@
         <v>23</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
@@ -9267,7 +9266,7 @@
         <v>333</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
@@ -9280,10 +9279,10 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B388" s="2" t="s">
         <v>1112</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
@@ -9291,7 +9290,7 @@
         <v>469</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
@@ -9299,15 +9298,15 @@
         <v>403</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B391" s="3" t="s">
         <v>1116</v>
-      </c>
-      <c r="B391" s="3" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
@@ -9315,15 +9314,15 @@
         <v>92</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B393" s="3" t="s">
         <v>1119</v>
-      </c>
-      <c r="B393" s="3" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
@@ -9331,7 +9330,7 @@
         <v>287</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
@@ -9339,7 +9338,7 @@
         <v>647</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
@@ -9347,63 +9346,63 @@
         <v>258</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A397" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B397" s="3" t="s">
         <v>1124</v>
-      </c>
-      <c r="B397" s="3" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A398" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B398" s="2" t="s">
         <v>1126</v>
-      </c>
-      <c r="B398" s="2" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A399" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B399" s="3" t="s">
         <v>1128</v>
-      </c>
-      <c r="B399" s="3" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A400" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B400" s="2" t="s">
         <v>1130</v>
-      </c>
-      <c r="B400" s="2" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A401" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B401" s="3" t="s">
         <v>1132</v>
-      </c>
-      <c r="B401" s="3" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A402" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B402" s="3" t="s">
         <v>1134</v>
-      </c>
-      <c r="B402" s="3" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A403" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B403" s="2" t="s">
         <v>1136</v>
-      </c>
-      <c r="B403" s="2" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
@@ -9411,23 +9410,23 @@
         <v>456</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A405" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B405" s="2" t="s">
         <v>1139</v>
-      </c>
-      <c r="B405" s="2" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A406" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B406" s="3" t="s">
         <v>1141</v>
-      </c>
-      <c r="B406" s="3" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
@@ -9435,15 +9434,15 @@
         <v>123</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A408" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B408" s="3" t="s">
         <v>1144</v>
-      </c>
-      <c r="B408" s="3" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
@@ -9451,7 +9450,7 @@
         <v>344</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
@@ -9459,23 +9458,23 @@
         <v>402</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A411" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B411" s="2" t="s">
         <v>1148</v>
-      </c>
-      <c r="B411" s="2" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A412" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B412" s="3" t="s">
         <v>1150</v>
-      </c>
-      <c r="B412" s="3" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
@@ -9483,7 +9482,7 @@
         <v>388</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
@@ -9496,26 +9495,26 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A415" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B415" s="2" t="s">
         <v>1153</v>
-      </c>
-      <c r="B415" s="2" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A416" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B416" s="3" t="s">
         <v>1155</v>
-      </c>
-      <c r="B416" s="3" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1157</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
@@ -9523,7 +9522,7 @@
         <v>590</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
@@ -9536,10 +9535,10 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A420" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B420" s="3" t="s">
         <v>1160</v>
-      </c>
-      <c r="B420" s="3" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
@@ -9547,7 +9546,7 @@
         <v>284</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
@@ -9555,7 +9554,7 @@
         <v>619</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
@@ -9568,18 +9567,18 @@
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A424" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B424" s="3" t="s">
         <v>1164</v>
-      </c>
-      <c r="B424" s="3" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A425" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B425" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="B425" s="2" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
@@ -9592,18 +9591,18 @@
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A427" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B427" s="3" t="s">
         <v>1168</v>
-      </c>
-      <c r="B427" s="3" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A428" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B428" s="2" t="s">
         <v>1170</v>
-      </c>
-      <c r="B428" s="2" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
@@ -9611,7 +9610,7 @@
         <v>487</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
@@ -9624,18 +9623,18 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A431" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B431" s="3" t="s">
         <v>1173</v>
-      </c>
-      <c r="B431" s="3" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A432" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B432" s="2" t="s">
         <v>1175</v>
-      </c>
-      <c r="B432" s="2" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
@@ -9643,7 +9642,7 @@
         <v>680</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
@@ -9651,7 +9650,7 @@
         <v>316</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
@@ -9683,7 +9682,7 @@
         <v>485</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
@@ -9704,26 +9703,26 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B441" s="3" t="s">
         <v>1180</v>
-      </c>
-      <c r="B441" s="3" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A442" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B442" s="2" t="s">
         <v>1182</v>
-      </c>
-      <c r="B442" s="2" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B443" s="3" t="s">
         <v>1184</v>
-      </c>
-      <c r="B443" s="3" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
@@ -9731,7 +9730,7 @@
         <v>638</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
@@ -9739,7 +9738,7 @@
         <v>260</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
@@ -9747,7 +9746,7 @@
         <v>503</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
@@ -9755,7 +9754,7 @@
         <v>396</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
@@ -9768,18 +9767,18 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A449" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B449" s="3" t="s">
         <v>1190</v>
-      </c>
-      <c r="B449" s="3" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A450" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B450" s="2" t="s">
         <v>1192</v>
-      </c>
-      <c r="B450" s="2" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
@@ -9787,15 +9786,15 @@
         <v>278</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A452" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B452" s="3" t="s">
         <v>1195</v>
-      </c>
-      <c r="B452" s="3" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
@@ -9803,7 +9802,7 @@
         <v>406</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
@@ -9816,10 +9815,10 @@
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A455" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B455" s="2" t="s">
         <v>1198</v>
-      </c>
-      <c r="B455" s="2" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
@@ -9827,7 +9826,7 @@
         <v>200</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
@@ -9843,39 +9842,39 @@
         <v>420</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A459" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B459" s="2" t="s">
         <v>1202</v>
-      </c>
-      <c r="B459" s="2" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A460" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B460" s="3" t="s">
         <v>1204</v>
-      </c>
-      <c r="B460" s="3" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A461" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B461" s="2" t="s">
         <v>1206</v>
-      </c>
-      <c r="B461" s="2" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A462" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B462" s="3" t="s">
         <v>1208</v>
-      </c>
-      <c r="B462" s="3" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
@@ -9883,23 +9882,23 @@
         <v>596</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A464" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B464" s="3" t="s">
         <v>1211</v>
-      </c>
-      <c r="B464" s="3" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A465" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B465" s="2" t="s">
         <v>1213</v>
-      </c>
-      <c r="B465" s="2" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
@@ -9907,7 +9906,7 @@
         <v>686</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
@@ -9915,15 +9914,15 @@
         <v>407</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A468" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B468" s="3" t="s">
         <v>1217</v>
-      </c>
-      <c r="B468" s="3" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
@@ -9931,7 +9930,7 @@
         <v>405</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
@@ -9944,18 +9943,18 @@
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A471" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B471" s="2" t="s">
         <v>1220</v>
-      </c>
-      <c r="B471" s="2" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A472" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B472" s="3" t="s">
         <v>1222</v>
-      </c>
-      <c r="B472" s="3" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
@@ -9963,23 +9962,23 @@
         <v>493</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A474" s="3" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A475" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B475" s="2" t="s">
         <v>1226</v>
-      </c>
-      <c r="B475" s="2" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
@@ -9995,15 +9994,15 @@
         <v>283</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A478" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B478" s="2" t="s">
         <v>1229</v>
-      </c>
-      <c r="B478" s="2" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
@@ -10011,15 +10010,15 @@
         <v>428</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A480" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B480" s="2" t="s">
         <v>1232</v>
-      </c>
-      <c r="B480" s="2" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
@@ -10027,7 +10026,7 @@
         <v>657</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
@@ -10035,7 +10034,7 @@
         <v>18</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
@@ -10043,15 +10042,15 @@
         <v>540</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B484" s="2" t="s">
         <v>1237</v>
-      </c>
-      <c r="B484" s="2" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
@@ -10059,7 +10058,7 @@
         <v>671</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
@@ -10067,7 +10066,7 @@
         <v>302</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
@@ -10075,15 +10074,15 @@
         <v>142</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A488" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B488" s="2" t="s">
         <v>1242</v>
-      </c>
-      <c r="B488" s="2" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
@@ -10099,15 +10098,15 @@
         <v>541</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A491" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B491" s="3" t="s">
         <v>1245</v>
-      </c>
-      <c r="B491" s="3" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
@@ -10123,23 +10122,23 @@
         <v>434</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A494" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B494" s="2" t="s">
         <v>1248</v>
-      </c>
-      <c r="B494" s="2" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A495" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B495" s="3" t="s">
         <v>1250</v>
-      </c>
-      <c r="B495" s="3" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
@@ -10147,7 +10146,7 @@
         <v>674</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
@@ -10155,7 +10154,7 @@
         <v>616</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
@@ -10163,7 +10162,7 @@
         <v>673</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
@@ -10176,10 +10175,10 @@
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A500" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B500" s="2" t="s">
         <v>1255</v>
-      </c>
-      <c r="B500" s="2" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
@@ -10203,15 +10202,15 @@
         <v>651</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A504" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B504" s="3" t="s">
         <v>1258</v>
-      </c>
-      <c r="B504" s="3" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
@@ -10219,15 +10218,15 @@
         <v>478</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A506" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B506" s="3" t="s">
         <v>1261</v>
-      </c>
-      <c r="B506" s="3" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
@@ -10235,7 +10234,7 @@
         <v>645</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
@@ -10243,7 +10242,7 @@
         <v>315</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
@@ -10251,15 +10250,15 @@
         <v>626</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A510" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B510" s="3" t="s">
         <v>1266</v>
-      </c>
-      <c r="B510" s="3" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
@@ -10267,7 +10266,7 @@
         <v>356</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
@@ -10275,31 +10274,31 @@
         <v>209</v>
       </c>
       <c r="B512" s="3" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A513" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B513" s="3" t="s">
         <v>1270</v>
-      </c>
-      <c r="B513" s="3" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B514" s="2" t="s">
         <v>1272</v>
-      </c>
-      <c r="B514" s="2" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B515" s="3" t="s">
         <v>1274</v>
-      </c>
-      <c r="B515" s="3" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
@@ -10315,7 +10314,7 @@
         <v>455</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
@@ -10323,7 +10322,7 @@
         <v>306</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
@@ -10339,15 +10338,15 @@
         <v>81</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B521" s="3" t="s">
         <v>1279</v>
-      </c>
-      <c r="B521" s="3" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
@@ -10355,7 +10354,7 @@
         <v>337</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
@@ -10363,7 +10362,7 @@
         <v>411</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
@@ -10376,15 +10375,15 @@
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B525" s="3" t="s">
         <v>1283</v>
-      </c>
-      <c r="B525" s="3" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" s="3" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B526" s="3" t="s">
         <v>117</v>
@@ -10403,7 +10402,7 @@
         <v>547</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
@@ -10416,42 +10415,42 @@
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B530" s="3" t="s">
         <v>1287</v>
-      </c>
-      <c r="B530" s="3" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B531" s="2" t="s">
         <v>1289</v>
-      </c>
-      <c r="B531" s="2" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B532" s="3" t="s">
         <v>1291</v>
-      </c>
-      <c r="B532" s="3" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B533" s="2" t="s">
         <v>1293</v>
-      </c>
-      <c r="B533" s="2" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B534" s="3" t="s">
         <v>1295</v>
-      </c>
-      <c r="B534" s="3" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
@@ -10459,7 +10458,7 @@
         <v>332</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
@@ -10467,47 +10466,47 @@
         <v>474</v>
       </c>
       <c r="B536" s="3" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B537" s="2" t="s">
         <v>1299</v>
-      </c>
-      <c r="B537" s="2" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B538" s="3" t="s">
         <v>1301</v>
-      </c>
-      <c r="B538" s="3" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B539" s="2" t="s">
         <v>1303</v>
-      </c>
-      <c r="B539" s="2" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B540" s="3" t="s">
         <v>1305</v>
-      </c>
-      <c r="B540" s="3" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B541" s="2" t="s">
         <v>1307</v>
-      </c>
-      <c r="B541" s="2" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
@@ -10515,7 +10514,7 @@
         <v>325</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
@@ -10523,7 +10522,7 @@
         <v>683</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
@@ -10531,15 +10530,15 @@
         <v>339</v>
       </c>
       <c r="B544" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B545" s="2" t="s">
         <v>1312</v>
-      </c>
-      <c r="B545" s="2" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
@@ -10547,31 +10546,31 @@
         <v>350</v>
       </c>
       <c r="B546" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B547" s="2" t="s">
         <v>1315</v>
-      </c>
-      <c r="B547" s="2" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B548" s="3" t="s">
         <v>1317</v>
-      </c>
-      <c r="B548" s="3" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B549" s="2" t="s">
         <v>1319</v>
-      </c>
-      <c r="B549" s="2" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
@@ -10579,7 +10578,7 @@
         <v>538</v>
       </c>
       <c r="B550" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
@@ -10587,7 +10586,7 @@
         <v>671</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
@@ -10595,7 +10594,7 @@
         <v>486</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
@@ -10603,15 +10602,15 @@
         <v>42</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B554" s="2" t="s">
         <v>1325</v>
-      </c>
-      <c r="B554" s="2" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
@@ -10619,7 +10618,7 @@
         <v>232</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
@@ -10627,7 +10626,7 @@
         <v>506</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
@@ -10635,15 +10634,15 @@
         <v>442</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B558" s="2" t="s">
         <v>1330</v>
-      </c>
-      <c r="B558" s="2" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
@@ -10651,31 +10650,31 @@
         <v>399</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B560" s="2" t="s">
         <v>1333</v>
-      </c>
-      <c r="B560" s="2" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B561" s="3" t="s">
         <v>1335</v>
-      </c>
-      <c r="B561" s="3" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B562" s="2" t="s">
         <v>1337</v>
-      </c>
-      <c r="B562" s="2" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
@@ -10691,7 +10690,7 @@
         <v>326</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
@@ -10699,7 +10698,7 @@
         <v>542</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
@@ -10707,23 +10706,23 @@
         <v>665</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B567" s="3" t="s">
         <v>1342</v>
-      </c>
-      <c r="B567" s="3" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B568" s="2" t="s">
         <v>1344</v>
-      </c>
-      <c r="B568" s="2" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.2">
@@ -10731,23 +10730,23 @@
         <v>222</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A570" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B570" s="2" t="s">
         <v>1347</v>
-      </c>
-      <c r="B570" s="2" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A571" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B571" s="3" t="s">
         <v>1349</v>
-      </c>
-      <c r="B571" s="3" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.2">
@@ -10755,23 +10754,23 @@
         <v>338</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A573" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B573" s="3" t="s">
         <v>1352</v>
-      </c>
-      <c r="B573" s="3" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A574" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B574" s="2" t="s">
         <v>1354</v>
-      </c>
-      <c r="B574" s="2" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.2">
@@ -10779,55 +10778,55 @@
         <v>662</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A576" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B576" s="3" t="s">
         <v>1357</v>
-      </c>
-      <c r="B576" s="3" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A577" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B577" s="2" t="s">
         <v>1359</v>
-      </c>
-      <c r="B577" s="2" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A578" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B578" s="3" t="s">
         <v>1361</v>
-      </c>
-      <c r="B578" s="3" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A579" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B579" s="2" t="s">
         <v>1363</v>
-      </c>
-      <c r="B579" s="2" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A580" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B580" s="3" t="s">
         <v>1365</v>
-      </c>
-      <c r="B580" s="3" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A581" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B581" s="2" t="s">
         <v>1367</v>
-      </c>
-      <c r="B581" s="2" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.2">
@@ -10835,12 +10834,12 @@
         <v>202</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A583" s="2" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>490</v>
@@ -10851,7 +10850,7 @@
         <v>78</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.2">
@@ -10864,26 +10863,26 @@
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A586" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B586" s="3" t="s">
         <v>1372</v>
-      </c>
-      <c r="B586" s="3" t="s">
-        <v>1373</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A587" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B587" s="2" t="s">
         <v>1374</v>
-      </c>
-      <c r="B587" s="2" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A588" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B588" s="3" t="s">
         <v>1376</v>
-      </c>
-      <c r="B588" s="3" t="s">
-        <v>1377</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.2">
@@ -10899,15 +10898,15 @@
         <v>340</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A591" s="2" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.2">
@@ -10923,23 +10922,23 @@
         <v>600</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A594" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A595" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B595" s="2" t="s">
         <v>1382</v>
-      </c>
-      <c r="B595" s="2" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.2">
@@ -10947,15 +10946,15 @@
         <v>441</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A597" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B597" s="2" t="s">
         <v>1385</v>
-      </c>
-      <c r="B597" s="2" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.2">
@@ -10992,18 +10991,18 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A602" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B602" s="2" t="s">
         <v>1387</v>
-      </c>
-      <c r="B602" s="2" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A603" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B603" s="3" t="s">
         <v>1389</v>
-      </c>
-      <c r="B603" s="3" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.2">
@@ -11011,7 +11010,7 @@
         <v>687</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.2">
@@ -11019,7 +11018,7 @@
         <v>401</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.2">
@@ -11027,7 +11026,7 @@
         <v>576</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.2">
@@ -11035,7 +11034,7 @@
         <v>654</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.2">
@@ -11043,15 +11042,15 @@
         <v>412</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A609" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B609" s="3" t="s">
         <v>1396</v>
-      </c>
-      <c r="B609" s="3" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.2">
@@ -11059,7 +11058,7 @@
         <v>52</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.2">
@@ -11067,12 +11066,12 @@
         <v>637</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A612" s="2" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>559</v>
@@ -11083,31 +11082,31 @@
         <v>393</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A614" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B614" s="2" t="s">
         <v>1402</v>
-      </c>
-      <c r="B614" s="2" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A615" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B615" s="3" t="s">
         <v>1404</v>
-      </c>
-      <c r="B615" s="3" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A616" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B616" s="2" t="s">
         <v>1406</v>
-      </c>
-      <c r="B616" s="2" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.2">
@@ -11120,10 +11119,10 @@
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A618" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.2">
@@ -11131,39 +11130,39 @@
         <v>605</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A620" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B620" s="2" t="s">
         <v>1410</v>
-      </c>
-      <c r="B620" s="2" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A621" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B621" s="3" t="s">
         <v>1412</v>
-      </c>
-      <c r="B621" s="3" t="s">
-        <v>1413</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A622" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B622" s="2" t="s">
         <v>1414</v>
-      </c>
-      <c r="B622" s="2" t="s">
-        <v>1415</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A623" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B623" s="3" t="s">
         <v>1416</v>
-      </c>
-      <c r="B623" s="3" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.2">
@@ -11179,7 +11178,7 @@
         <v>597</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.2">
@@ -11187,7 +11186,7 @@
         <v>623</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.2">
@@ -11195,7 +11194,7 @@
         <v>331</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.2">
@@ -11203,12 +11202,12 @@
         <v>305</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A629" s="2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>684</v>
@@ -11216,10 +11215,10 @@
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A630" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B630" s="3" t="s">
         <v>1423</v>
-      </c>
-      <c r="B630" s="3" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.2">
@@ -11232,50 +11231,50 @@
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A632" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B632" s="3" t="s">
         <v>1425</v>
-      </c>
-      <c r="B632" s="3" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A633" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B633" s="2" t="s">
         <v>1427</v>
-      </c>
-      <c r="B633" s="2" t="s">
-        <v>1428</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A634" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B634" s="3" t="s">
         <v>1429</v>
-      </c>
-      <c r="B634" s="3" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A635" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B635" s="2" t="s">
         <v>1431</v>
-      </c>
-      <c r="B635" s="2" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A636" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B636" s="3" t="s">
         <v>1433</v>
-      </c>
-      <c r="B636" s="3" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A637" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B637" s="2" t="s">
         <v>1435</v>
-      </c>
-      <c r="B637" s="2" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.2">
@@ -11283,7 +11282,7 @@
         <v>71</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.2">
@@ -11291,7 +11290,7 @@
         <v>257</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.2">
@@ -11315,7 +11314,7 @@
         <v>549</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.2">
@@ -11323,39 +11322,39 @@
         <v>627</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A644" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B644" s="3" t="s">
         <v>1440</v>
-      </c>
-      <c r="B644" s="3" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A645" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B645" s="2" t="s">
         <v>1442</v>
-      </c>
-      <c r="B645" s="2" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A646" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B646" s="3" t="s">
         <v>1444</v>
-      </c>
-      <c r="B646" s="3" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A647" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B647" s="2" t="s">
         <v>1446</v>
-      </c>
-      <c r="B647" s="2" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.2">
@@ -11363,7 +11362,7 @@
         <v>584</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.2">
@@ -11371,7 +11370,7 @@
         <v>444</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.2">
@@ -11379,23 +11378,23 @@
         <v>33</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A651" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B651" s="3" t="s">
         <v>1451</v>
-      </c>
-      <c r="B651" s="3" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A652" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B652" s="2" t="s">
         <v>1453</v>
-      </c>
-      <c r="B652" s="2" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.2">
@@ -11403,7 +11402,7 @@
         <v>512</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.2">
@@ -11411,28 +11410,28 @@
         <v>169</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A655" s="3" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A656" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B656" s="2" t="s">
         <v>1458</v>
-      </c>
-      <c r="B656" s="2" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A657" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B657" s="3" t="s">
         <v>561</v>
@@ -11440,114 +11439,114 @@
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A658" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B658" s="2" t="s">
         <v>1461</v>
-      </c>
-      <c r="B658" s="2" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A659" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B659" s="3" t="s">
         <v>1463</v>
-      </c>
-      <c r="B659" s="3" t="s">
-        <v>1464</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A660" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B660" s="2" t="s">
         <v>1465</v>
-      </c>
-      <c r="B660" s="2" t="s">
-        <v>1466</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A661" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B661" s="3" t="s">
         <v>1467</v>
-      </c>
-      <c r="B661" s="3" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A662" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B662" s="2" t="s">
         <v>1469</v>
-      </c>
-      <c r="B662" s="2" t="s">
-        <v>1470</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A663" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B663" s="3" t="s">
         <v>1471</v>
-      </c>
-      <c r="B663" s="3" t="s">
-        <v>1472</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A664" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B664" s="2" t="s">
         <v>1473</v>
-      </c>
-      <c r="B664" s="2" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A665" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B665" s="3" t="s">
         <v>1475</v>
-      </c>
-      <c r="B665" s="3" t="s">
-        <v>1476</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A666" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B666" s="2" t="s">
         <v>1477</v>
-      </c>
-      <c r="B666" s="2" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A667" s="3" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B667" s="3" t="s">
         <v>1479</v>
-      </c>
-      <c r="B667" s="3" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A668" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B668" s="2" t="s">
         <v>1481</v>
-      </c>
-      <c r="B668" s="2" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A669" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B669" s="3" t="s">
         <v>1483</v>
-      </c>
-      <c r="B669" s="3" t="s">
-        <v>1484</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A670" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B670" s="2" t="s">
         <v>1485</v>
-      </c>
-      <c r="B670" s="2" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A671" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B671" s="3" t="s">
         <v>1487</v>
-      </c>
-      <c r="B671" s="3" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.2">
@@ -11555,23 +11554,23 @@
         <v>639</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A673" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B673" s="3" t="s">
         <v>1490</v>
-      </c>
-      <c r="B673" s="3" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A674" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B674" s="2" t="s">
         <v>1492</v>
-      </c>
-      <c r="B674" s="2" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.2">
@@ -11579,7 +11578,7 @@
         <v>408</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.2">
@@ -11587,7 +11586,7 @@
         <v>646</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.2">
@@ -11595,7 +11594,7 @@
         <v>347</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.2">
@@ -11608,18 +11607,18 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A679" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B679" s="2" t="s">
         <v>1497</v>
-      </c>
-      <c r="B679" s="2" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A680" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B680" s="3" t="s">
         <v>1499</v>
-      </c>
-      <c r="B680" s="3" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.2">
@@ -11635,7 +11634,7 @@
         <v>606</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.2">
@@ -11643,7 +11642,7 @@
         <v>519</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.2">
@@ -11651,23 +11650,23 @@
         <v>603</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A685" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B685" s="2" t="s">
         <v>1504</v>
-      </c>
-      <c r="B685" s="2" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A686" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B686" s="3" t="s">
         <v>1506</v>
-      </c>
-      <c r="B686" s="3" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.2">
@@ -11675,7 +11674,7 @@
         <v>448</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.2">
@@ -11683,7 +11682,7 @@
         <v>520</v>
       </c>
       <c r="B688" s="3" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.2">
@@ -11691,7 +11690,7 @@
         <v>281</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.2">
@@ -11704,10 +11703,10 @@
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A691" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B691" s="2" t="s">
         <v>1511</v>
-      </c>
-      <c r="B691" s="2" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.2">
@@ -11715,7 +11714,7 @@
         <v>164</v>
       </c>
       <c r="B692" s="3" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.2">
@@ -11723,15 +11722,15 @@
         <v>314</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A694" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B694" s="3" t="s">
         <v>1515</v>
-      </c>
-      <c r="B694" s="3" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.2">
@@ -11739,31 +11738,31 @@
         <v>593</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A696" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B696" s="3" t="s">
         <v>1518</v>
-      </c>
-      <c r="B696" s="3" t="s">
-        <v>1519</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A697" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B697" s="2" t="s">
         <v>1520</v>
-      </c>
-      <c r="B697" s="2" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A698" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B698" s="3" t="s">
         <v>1522</v>
-      </c>
-      <c r="B698" s="3" t="s">
-        <v>1523</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.2">
@@ -11771,15 +11770,15 @@
         <v>656</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A700" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B700" s="2" t="s">
         <v>1525</v>
-      </c>
-      <c r="B700" s="2" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.2">
@@ -11792,10 +11791,10 @@
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A702" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B702" s="2" t="s">
         <v>1527</v>
-      </c>
-      <c r="B702" s="2" t="s">
-        <v>1528</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.2">
@@ -11803,7 +11802,7 @@
         <v>184</v>
       </c>
       <c r="B703" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.2">
@@ -11811,15 +11810,15 @@
         <v>625</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A705" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B705" s="3" t="s">
         <v>1531</v>
-      </c>
-      <c r="B705" s="3" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.2">
@@ -11827,7 +11826,7 @@
         <v>370</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.2">
@@ -11835,23 +11834,23 @@
         <v>636</v>
       </c>
       <c r="B707" s="3" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A708" s="2" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B708" s="2" t="s">
         <v>1535</v>
-      </c>
-      <c r="B708" s="2" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A709" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B709" s="3" t="s">
         <v>1537</v>
-      </c>
-      <c r="B709" s="3" t="s">
-        <v>1538</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.2">
@@ -11859,7 +11858,7 @@
         <v>580</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.2">
@@ -11867,7 +11866,7 @@
         <v>317</v>
       </c>
       <c r="B711" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.2">
@@ -11899,15 +11898,15 @@
         <v>595</v>
       </c>
       <c r="B715" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A716" s="2" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.2">
@@ -11920,10 +11919,10 @@
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A718" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B718" s="2" t="s">
         <v>1543</v>
-      </c>
-      <c r="B718" s="2" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.2">
@@ -11931,7 +11930,7 @@
         <v>99</v>
       </c>
       <c r="B719" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.2">
@@ -11939,39 +11938,39 @@
         <v>244</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A721" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B721" s="3" t="s">
         <v>1547</v>
-      </c>
-      <c r="B721" s="3" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A722" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B722" s="2" t="s">
         <v>1549</v>
-      </c>
-      <c r="B722" s="2" t="s">
-        <v>1550</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A723" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B723" s="3" t="s">
         <v>1551</v>
-      </c>
-      <c r="B723" s="3" t="s">
-        <v>1552</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A724" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B724" s="2" t="s">
         <v>1553</v>
-      </c>
-      <c r="B724" s="2" t="s">
-        <v>1554</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.2">
@@ -11987,23 +11986,23 @@
         <v>334</v>
       </c>
       <c r="B726" s="3" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A727" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B727" s="2" t="s">
         <v>1556</v>
-      </c>
-      <c r="B727" s="2" t="s">
-        <v>1557</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A728" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B728" s="3" t="s">
         <v>1558</v>
-      </c>
-      <c r="B728" s="3" t="s">
-        <v>1559</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.2">
@@ -12016,26 +12015,26 @@
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A730" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B730" s="3" t="s">
         <v>1560</v>
-      </c>
-      <c r="B730" s="3" t="s">
-        <v>1561</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A731" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B731" s="2" t="s">
         <v>1562</v>
-      </c>
-      <c r="B731" s="2" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A732" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B732" s="3" t="s">
         <v>1564</v>
-      </c>
-      <c r="B732" s="3" t="s">
-        <v>1565</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.2">
@@ -12043,7 +12042,7 @@
         <v>669</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.2">
@@ -12051,7 +12050,7 @@
         <v>573</v>
       </c>
       <c r="B734" s="3" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.2">
@@ -12059,15 +12058,15 @@
         <v>303</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A736" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B736" s="3" t="s">
         <v>1569</v>
-      </c>
-      <c r="B736" s="3" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.2">
@@ -12083,7 +12082,7 @@
         <v>416</v>
       </c>
       <c r="B738" s="3" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.2">
@@ -12091,15 +12090,15 @@
         <v>170</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A740" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B740" s="3" t="s">
         <v>1573</v>
-      </c>
-      <c r="B740" s="3" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.2">
@@ -12107,7 +12106,7 @@
         <v>510</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.2">
@@ -12115,23 +12114,23 @@
         <v>214</v>
       </c>
       <c r="B742" s="3" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A743" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B743" s="2" t="s">
         <v>1577</v>
-      </c>
-      <c r="B743" s="2" t="s">
-        <v>1578</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A744" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B744" s="3" t="s">
         <v>1579</v>
-      </c>
-      <c r="B744" s="3" t="s">
-        <v>1580</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.2">
@@ -12147,7 +12146,7 @@
         <v>666</v>
       </c>
       <c r="B746" s="3" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.2">
@@ -12155,7 +12154,7 @@
         <v>675</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.2">
@@ -12168,10 +12167,10 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A749" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B749" s="2" t="s">
         <v>1583</v>
-      </c>
-      <c r="B749" s="2" t="s">
-        <v>1584</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.2">
@@ -12184,18 +12183,18 @@
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A751" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B751" s="3" t="s">
         <v>1585</v>
-      </c>
-      <c r="B751" s="3" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A752" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B752" s="2" t="s">
         <v>1587</v>
-      </c>
-      <c r="B752" s="2" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.2">
@@ -12211,15 +12210,15 @@
         <v>384</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A755" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B755" s="3" t="s">
         <v>1590</v>
-      </c>
-      <c r="B755" s="3" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.2">
@@ -12227,7 +12226,7 @@
         <v>100</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.2">
@@ -12235,15 +12234,15 @@
         <v>630</v>
       </c>
       <c r="B757" s="3" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A758" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B758" s="2" t="s">
         <v>1594</v>
-      </c>
-      <c r="B758" s="2" t="s">
-        <v>1595</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.2">
@@ -12251,23 +12250,23 @@
         <v>413</v>
       </c>
       <c r="B759" s="3" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A760" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B760" s="2" t="s">
         <v>1597</v>
-      </c>
-      <c r="B760" s="2" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A761" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B761" s="3" t="s">
         <v>1599</v>
-      </c>
-      <c r="B761" s="3" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.2">
@@ -12275,28 +12274,28 @@
         <v>568</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A763" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B763" s="3" t="s">
         <v>1602</v>
-      </c>
-      <c r="B763" s="3" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A764" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B764" s="2" t="s">
         <v>1604</v>
-      </c>
-      <c r="B764" s="2" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A765" s="3" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B765" s="3" t="s">
         <v>233</v>
@@ -12307,12 +12306,12 @@
         <v>504</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A767" s="3" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="B767" s="3" t="s">
         <v>650</v>
@@ -12320,26 +12319,26 @@
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A768" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B768" s="2" t="s">
         <v>1609</v>
-      </c>
-      <c r="B768" s="2" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A769" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B769" s="3" t="s">
         <v>1611</v>
-      </c>
-      <c r="B769" s="3" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A770" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B770" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="B770" s="2" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.2">
@@ -12347,23 +12346,23 @@
         <v>511</v>
       </c>
       <c r="B771" s="3" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A772" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B772" s="2" t="s">
         <v>1616</v>
-      </c>
-      <c r="B772" s="2" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A773" s="3" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B773" s="3" t="s">
         <v>1618</v>
-      </c>
-      <c r="B773" s="3" t="s">
-        <v>1619</v>
       </c>
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.2">
@@ -12376,10 +12375,10 @@
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A775" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B775" s="2" t="s">
         <v>1620</v>
-      </c>
-      <c r="B775" s="2" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.2">
@@ -12395,7 +12394,7 @@
         <v>201</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.2">
@@ -12403,7 +12402,7 @@
         <v>622</v>
       </c>
       <c r="B778" s="3" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.2">
@@ -12411,47 +12410,47 @@
         <v>79</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A780" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B780" s="3" t="s">
         <v>1625</v>
-      </c>
-      <c r="B780" s="3" t="s">
-        <v>1626</v>
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A781" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B781" s="2" t="s">
         <v>1627</v>
-      </c>
-      <c r="B781" s="2" t="s">
-        <v>1628</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A782" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B782" s="3" t="s">
         <v>1629</v>
-      </c>
-      <c r="B782" s="3" t="s">
-        <v>1630</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A783" s="2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B783" s="2" t="s">
         <v>1631</v>
-      </c>
-      <c r="B783" s="2" t="s">
-        <v>1632</v>
       </c>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A784" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B784" s="3" t="s">
         <v>1633</v>
-      </c>
-      <c r="B784" s="3" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.2">
@@ -12459,15 +12458,15 @@
         <v>539</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A786" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B786" s="3" t="s">
         <v>1635</v>
-      </c>
-      <c r="B786" s="3" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.2">
@@ -12475,44 +12474,44 @@
         <v>290</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A788" s="3" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B788" s="3" t="s">
         <v>1638</v>
-      </c>
-      <c r="B788" s="3" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A789" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B789" s="2" t="s">
         <v>1640</v>
-      </c>
-      <c r="B789" s="2" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A790" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B790" s="3" t="s">
         <v>1642</v>
-      </c>
-      <c r="B790" s="3" t="s">
-        <v>1643</v>
       </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A791" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B791" s="2" t="s">
         <v>1644</v>
-      </c>
-      <c r="B791" s="2" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A792" s="3" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="B792" s="3" t="s">
         <v>492</v>
@@ -12520,34 +12519,34 @@
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A793" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B793" s="2" t="s">
         <v>1647</v>
-      </c>
-      <c r="B793" s="2" t="s">
-        <v>1648</v>
       </c>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A794" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B794" s="3" t="s">
         <v>1649</v>
-      </c>
-      <c r="B794" s="3" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A795" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B795" s="2" t="s">
         <v>1651</v>
-      </c>
-      <c r="B795" s="2" t="s">
-        <v>1652</v>
       </c>
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A796" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B796" s="3" t="s">
         <v>1653</v>
-      </c>
-      <c r="B796" s="3" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.2">
@@ -12555,23 +12554,23 @@
         <v>624</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A798" s="3" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B798" s="3" t="s">
         <v>1656</v>
-      </c>
-      <c r="B798" s="3" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A799" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B799" s="2" t="s">
         <v>1658</v>
-      </c>
-      <c r="B799" s="2" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.2">
@@ -12579,39 +12578,39 @@
         <v>672</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A801" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B801" s="3" t="s">
         <v>1661</v>
-      </c>
-      <c r="B801" s="3" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A802" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B802" s="2" t="s">
         <v>1663</v>
-      </c>
-      <c r="B802" s="2" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A803" s="3" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B803" s="3" t="s">
         <v>1665</v>
-      </c>
-      <c r="B803" s="3" t="s">
-        <v>1666</v>
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A804" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B804" s="2" t="s">
         <v>1667</v>
-      </c>
-      <c r="B804" s="2" t="s">
-        <v>1668</v>
       </c>
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.2">
@@ -12619,7 +12618,7 @@
         <v>648</v>
       </c>
       <c r="B805" s="3" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.2">
@@ -12627,15 +12626,15 @@
         <v>658</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A807" s="3" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B807" s="3" t="s">
         <v>1671</v>
-      </c>
-      <c r="B807" s="3" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.2">
@@ -12643,15 +12642,15 @@
         <v>313</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A809" s="3" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B809" s="3" t="s">
         <v>1674</v>
-      </c>
-      <c r="B809" s="3" t="s">
-        <v>1675</v>
       </c>
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.2">
@@ -12659,7 +12658,7 @@
         <v>589</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.2">
@@ -12672,10 +12671,10 @@
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A812" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B812" s="2" t="s">
         <v>1677</v>
-      </c>
-      <c r="B812" s="2" t="s">
-        <v>1678</v>
       </c>
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.2">
@@ -12696,23 +12695,23 @@
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A815" s="3" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B815" s="3" t="s">
         <v>1679</v>
-      </c>
-      <c r="B815" s="3" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A816" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B816" s="2" t="s">
         <v>1681</v>
-      </c>
-      <c r="B816" s="2" t="s">
-        <v>1682</v>
       </c>
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A817" s="3" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B817" s="3" t="s">
         <v>609</v>
@@ -12731,7 +12730,7 @@
         <v>509</v>
       </c>
       <c r="B819" s="3" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.2">
@@ -12739,7 +12738,7 @@
         <v>533</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.2">
@@ -12747,39 +12746,39 @@
         <v>570</v>
       </c>
       <c r="B821" s="3" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A822" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B822" s="2" t="s">
         <v>1687</v>
-      </c>
-      <c r="B822" s="2" t="s">
-        <v>1688</v>
       </c>
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A823" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B823" s="3" t="s">
         <v>1689</v>
-      </c>
-      <c r="B823" s="3" t="s">
-        <v>1690</v>
       </c>
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A824" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B824" s="2" t="s">
         <v>1691</v>
-      </c>
-      <c r="B824" s="2" t="s">
-        <v>1692</v>
       </c>
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A825" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B825" s="2" t="s">
         <v>1693</v>
-      </c>
-      <c r="B825" s="2" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.2">
@@ -12787,12 +12786,12 @@
         <v>298</v>
       </c>
       <c r="B826" s="3" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A827" s="2" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="B827" s="2" t="s">
         <v>72</v>
@@ -12800,7 +12799,7 @@
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A828" s="3" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="B828" s="3" t="s">
         <v>556</v>
@@ -12808,18 +12807,18 @@
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A829" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B829" s="2" t="s">
         <v>1698</v>
-      </c>
-      <c r="B829" s="2" t="s">
-        <v>1699</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A830" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B830" s="3" t="s">
         <v>1700</v>
-      </c>
-      <c r="B830" s="3" t="s">
-        <v>1701</v>
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.2">
@@ -12840,31 +12839,31 @@
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A833" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B833" s="2" t="s">
         <v>1702</v>
-      </c>
-      <c r="B833" s="2" t="s">
-        <v>1703</v>
       </c>
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A834" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B834" s="3" t="s">
         <v>1704</v>
-      </c>
-      <c r="B834" s="3" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A835" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B835" s="2" t="s">
         <v>1706</v>
-      </c>
-      <c r="B835" s="2" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A836" s="3" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="B836" s="3" t="s">
         <v>96</v>
@@ -12872,10 +12871,10 @@
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A837" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B837" s="2" t="s">
         <v>1709</v>
-      </c>
-      <c r="B837" s="2" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.2">
@@ -12888,31 +12887,31 @@
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A839" s="2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B839" s="2" t="s">
         <v>1711</v>
-      </c>
-      <c r="B839" s="2" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A840" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B840" s="3" t="s">
         <v>1713</v>
-      </c>
-      <c r="B840" s="3" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A841" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B841" s="2" t="s">
         <v>1715</v>
-      </c>
-      <c r="B841" s="2" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A842" s="3" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="B842" s="3" t="s">
         <v>551</v>
@@ -12920,50 +12919,50 @@
     </row>
     <row r="843" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A843" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B843" s="2" t="s">
         <v>1718</v>
-      </c>
-      <c r="B843" s="2" t="s">
-        <v>1719</v>
       </c>
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A844" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B844" s="3" t="s">
         <v>1720</v>
-      </c>
-      <c r="B844" s="3" t="s">
-        <v>1721</v>
       </c>
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A845" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B845" s="2" t="s">
         <v>1722</v>
-      </c>
-      <c r="B845" s="2" t="s">
-        <v>1723</v>
       </c>
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A846" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B846" s="3" t="s">
         <v>1724</v>
-      </c>
-      <c r="B846" s="3" t="s">
-        <v>1725</v>
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A847" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B847" s="2" t="s">
         <v>1726</v>
-      </c>
-      <c r="B847" s="2" t="s">
-        <v>1727</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A848" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B848" s="3" t="s">
         <v>1728</v>
-      </c>
-      <c r="B848" s="3" t="s">
-        <v>1729</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.2">
@@ -12971,31 +12970,31 @@
         <v>468</v>
       </c>
       <c r="B849" s="2" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A850" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B850" s="2" t="s">
         <v>1731</v>
-      </c>
-      <c r="B850" s="2" t="s">
-        <v>1732</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A851" s="3" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B851" s="3" t="s">
         <v>1733</v>
-      </c>
-      <c r="B851" s="3" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A852" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B852" s="2" t="s">
         <v>1735</v>
-      </c>
-      <c r="B852" s="2" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.2">
@@ -13003,15 +13002,15 @@
         <v>601</v>
       </c>
       <c r="B853" s="3" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A854" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B854" s="2" t="s">
         <v>1738</v>
-      </c>
-      <c r="B854" s="2" t="s">
-        <v>1739</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.2">
@@ -13019,15 +13018,15 @@
         <v>82</v>
       </c>
       <c r="B855" s="3" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A856" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B856" s="2" t="s">
         <v>1741</v>
-      </c>
-      <c r="B856" s="2" t="s">
-        <v>1742</v>
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.2">
@@ -13035,12 +13034,12 @@
         <v>118</v>
       </c>
       <c r="B857" s="3" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A858" s="2" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B858" s="2" t="s">
         <v>563</v>
@@ -13048,26 +13047,26 @@
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A859" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B859" s="3" t="s">
         <v>1745</v>
-      </c>
-      <c r="B859" s="3" t="s">
-        <v>1746</v>
       </c>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A860" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B860" s="2" t="s">
         <v>1747</v>
-      </c>
-      <c r="B860" s="2" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A861" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B861" s="3" t="s">
         <v>1749</v>
-      </c>
-      <c r="B861" s="3" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.2">
@@ -13075,31 +13074,31 @@
         <v>543</v>
       </c>
       <c r="B862" s="2" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A863" s="3" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B863" s="3" t="s">
         <v>1752</v>
-      </c>
-      <c r="B863" s="3" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A864" s="2" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B864" s="2" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A865" s="3" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B865" s="3" t="s">
         <v>1755</v>
-      </c>
-      <c r="B865" s="3" t="s">
-        <v>1756</v>
       </c>
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.2">
@@ -13107,23 +13106,23 @@
         <v>204</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A867" s="3" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B867" s="3" t="s">
         <v>1758</v>
-      </c>
-      <c r="B867" s="3" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A868" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B868" s="2" t="s">
         <v>1760</v>
-      </c>
-      <c r="B868" s="2" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.2">
@@ -13131,7 +13130,7 @@
         <v>415</v>
       </c>
       <c r="B869" s="3" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.2">
@@ -13139,15 +13138,15 @@
         <v>505</v>
       </c>
       <c r="B870" s="2" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A871" s="3" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B871" s="3" t="s">
         <v>1764</v>
-      </c>
-      <c r="B871" s="3" t="s">
-        <v>1765</v>
       </c>
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.2">
@@ -13160,18 +13159,18 @@
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A873" s="3" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B873" s="3" t="s">
         <v>1766</v>
-      </c>
-      <c r="B873" s="3" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A874" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B874" s="2" t="s">
         <v>1768</v>
-      </c>
-      <c r="B874" s="2" t="s">
-        <v>1769</v>
       </c>
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.2">
@@ -13179,7 +13178,7 @@
         <v>567</v>
       </c>
       <c r="B875" s="2" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="876" spans="1:2" x14ac:dyDescent="0.2">
@@ -13187,7 +13186,7 @@
         <v>277</v>
       </c>
       <c r="B876" s="3" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.2">
@@ -13200,23 +13199,23 @@
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A878" s="3" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B878" s="3" t="s">
         <v>1772</v>
-      </c>
-      <c r="B878" s="3" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A879" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B879" s="2" t="s">
         <v>1774</v>
-      </c>
-      <c r="B879" s="2" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A880" s="3" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="B880" s="3" t="s">
         <v>106</v>
@@ -13224,18 +13223,18 @@
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A881" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B881" s="2" t="s">
         <v>1777</v>
-      </c>
-      <c r="B881" s="2" t="s">
-        <v>1778</v>
       </c>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A882" s="3" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B882" s="3" t="s">
         <v>1779</v>
-      </c>
-      <c r="B882" s="3" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.2">
@@ -13243,15 +13242,15 @@
         <v>98</v>
       </c>
       <c r="B883" s="2" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A884" s="3" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B884" s="3" t="s">
         <v>1782</v>
-      </c>
-      <c r="B884" s="3" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.2">
@@ -13259,7 +13258,7 @@
         <v>475</v>
       </c>
       <c r="B885" s="2" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.2">
@@ -13267,15 +13266,15 @@
         <v>629</v>
       </c>
       <c r="B886" s="3" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="887" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A887" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B887" s="2" t="s">
         <v>1786</v>
-      </c>
-      <c r="B887" s="2" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.2">
@@ -13283,15 +13282,15 @@
         <v>301</v>
       </c>
       <c r="B888" s="3" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A889" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B889" s="2" t="s">
         <v>1789</v>
-      </c>
-      <c r="B889" s="2" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="890" spans="1:2" x14ac:dyDescent="0.2">
@@ -13299,7 +13298,7 @@
         <v>628</v>
       </c>
       <c r="B890" s="3" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="891" spans="1:2" x14ac:dyDescent="0.2">
@@ -13307,7 +13306,7 @@
         <v>410</v>
       </c>
       <c r="B891" s="2" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="892" spans="1:2" x14ac:dyDescent="0.2">
@@ -13315,20 +13314,20 @@
         <v>688</v>
       </c>
       <c r="B892" s="3" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A893" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B893" s="2" t="s">
         <v>1794</v>
-      </c>
-      <c r="B893" s="2" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A894" s="3" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B894" s="3" t="s">
         <v>102</v>
@@ -13336,90 +13335,90 @@
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A895" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B895" s="2" t="s">
         <v>1797</v>
-      </c>
-      <c r="B895" s="2" t="s">
-        <v>1798</v>
       </c>
     </row>
     <row r="896" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A896" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B896" s="3" t="s">
         <v>1799</v>
-      </c>
-      <c r="B896" s="3" t="s">
-        <v>1800</v>
       </c>
     </row>
     <row r="897" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A897" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B897" s="2" t="s">
         <v>1801</v>
-      </c>
-      <c r="B897" s="2" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A898" s="3" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B898" s="3" t="s">
         <v>1803</v>
-      </c>
-      <c r="B898" s="3" t="s">
-        <v>1804</v>
       </c>
     </row>
     <row r="899" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A899" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B899" s="2" t="s">
         <v>1805</v>
-      </c>
-      <c r="B899" s="2" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A900" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B900" s="2" t="s">
         <v>1807</v>
-      </c>
-      <c r="B900" s="2" t="s">
-        <v>1808</v>
       </c>
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A901" s="3" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B901" s="3" t="s">
         <v>1809</v>
-      </c>
-      <c r="B901" s="3" t="s">
-        <v>1810</v>
       </c>
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A902" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B902" s="2" t="s">
         <v>1811</v>
-      </c>
-      <c r="B902" s="2" t="s">
-        <v>1812</v>
       </c>
     </row>
     <row r="903" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A903" s="3" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B903" s="3" t="s">
         <v>1813</v>
-      </c>
-      <c r="B903" s="3" t="s">
-        <v>1814</v>
       </c>
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A904" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B904" s="2" t="s">
         <v>1815</v>
-      </c>
-      <c r="B904" s="2" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A905" s="3" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B905" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.2">
@@ -13427,23 +13426,23 @@
         <v>631</v>
       </c>
       <c r="B906" s="2" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A907" s="3" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B907" s="3" t="s">
         <v>1819</v>
-      </c>
-      <c r="B907" s="3" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="908" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A908" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B908" s="2" t="s">
         <v>1821</v>
-      </c>
-      <c r="B908" s="2" t="s">
-        <v>1822</v>
       </c>
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.2">
@@ -13451,23 +13450,23 @@
         <v>261</v>
       </c>
       <c r="B909" s="3" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A910" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B910" s="2" t="s">
         <v>1824</v>
-      </c>
-      <c r="B910" s="2" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A911" s="3" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B911" s="3" t="s">
         <v>1826</v>
-      </c>
-      <c r="B911" s="3" t="s">
-        <v>1827</v>
       </c>
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.2">
@@ -13475,12 +13474,12 @@
         <v>546</v>
       </c>
       <c r="B912" s="2" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A913" s="3" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="B913" s="3" t="s">
         <v>598</v>
@@ -13488,34 +13487,34 @@
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A914" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B914" s="2" t="s">
         <v>1830</v>
-      </c>
-      <c r="B914" s="2" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A915" s="3" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B915" s="3" t="s">
         <v>1832</v>
-      </c>
-      <c r="B915" s="3" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A916" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B916" s="2" t="s">
         <v>1834</v>
-      </c>
-      <c r="B916" s="2" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A917" s="3" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B917" s="3" t="s">
         <v>1836</v>
-      </c>
-      <c r="B917" s="3" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.2">
@@ -13523,63 +13522,63 @@
         <v>591</v>
       </c>
       <c r="B918" s="2" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A919" s="3" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B919" s="3" t="s">
         <v>1839</v>
-      </c>
-      <c r="B919" s="3" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A920" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B920" s="2" t="s">
         <v>1841</v>
-      </c>
-      <c r="B920" s="2" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A921" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B921" s="3" t="s">
         <v>1843</v>
-      </c>
-      <c r="B921" s="3" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A922" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B922" s="2" t="s">
         <v>1845</v>
-      </c>
-      <c r="B922" s="2" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A923" s="3" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B923" s="3" t="s">
         <v>1847</v>
-      </c>
-      <c r="B923" s="3" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A924" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B924" s="2" t="s">
         <v>1849</v>
-      </c>
-      <c r="B924" s="2" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A925" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B925" s="2" t="s">
         <v>1851</v>
-      </c>
-      <c r="B925" s="2" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.2">
@@ -13587,7 +13586,7 @@
         <v>602</v>
       </c>
       <c r="B926" s="3" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.2">
@@ -13595,7 +13594,7 @@
         <v>507</v>
       </c>
       <c r="B927" s="2" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.2">
@@ -13619,7 +13618,7 @@
         <v>349</v>
       </c>
       <c r="B930" s="3" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.2">
@@ -13627,15 +13626,15 @@
         <v>632</v>
       </c>
       <c r="B931" s="2" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A932" s="3" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B932" s="3" t="s">
         <v>1857</v>
-      </c>
-      <c r="B932" s="3" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.2">
@@ -13643,12 +13642,12 @@
         <v>57</v>
       </c>
       <c r="B933" s="2" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A934" s="3" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="B934" s="3" t="s">
         <v>682</v>
@@ -13659,15 +13658,15 @@
         <v>470</v>
       </c>
       <c r="B935" s="2" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A936" s="3" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B936" s="3" t="s">
         <v>1862</v>
-      </c>
-      <c r="B936" s="3" t="s">
-        <v>1863</v>
       </c>
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.2">
@@ -13675,15 +13674,15 @@
         <v>484</v>
       </c>
       <c r="B937" s="2" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A938" s="3" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B938" s="3" t="s">
         <v>1865</v>
-      </c>
-      <c r="B938" s="3" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="939" spans="1:2" x14ac:dyDescent="0.2">
@@ -13691,23 +13690,23 @@
         <v>670</v>
       </c>
       <c r="B939" s="2" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A940" s="3" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B940" s="3" t="s">
         <v>1868</v>
-      </c>
-      <c r="B940" s="3" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A941" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B941" s="2" t="s">
         <v>1870</v>
-      </c>
-      <c r="B941" s="2" t="s">
-        <v>1871</v>
       </c>
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.2">
@@ -13715,7 +13714,7 @@
         <v>477</v>
       </c>
       <c r="B942" s="3" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.2">
@@ -13728,31 +13727,31 @@
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A944" s="3" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B944" s="3" t="s">
         <v>1873</v>
-      </c>
-      <c r="B944" s="3" t="s">
-        <v>1874</v>
       </c>
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A945" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B945" s="2" t="s">
         <v>1875</v>
-      </c>
-      <c r="B945" s="2" t="s">
-        <v>1876</v>
       </c>
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A946" s="3" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B946" s="3" t="s">
         <v>1877</v>
-      </c>
-      <c r="B946" s="3" t="s">
-        <v>1878</v>
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A947" s="2" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="B947" s="2" t="s">
         <v>552</v>
@@ -13760,26 +13759,26 @@
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A948" s="3" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="B948" s="3" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="949" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A949" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B949" s="2" t="s">
         <v>1881</v>
-      </c>
-      <c r="B949" s="2" t="s">
-        <v>1882</v>
       </c>
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A950" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B950" s="2" t="s">
         <v>1883</v>
-      </c>
-      <c r="B950" s="2" t="s">
-        <v>1884</v>
       </c>
     </row>
     <row r="951" spans="1:2" x14ac:dyDescent="0.2">
@@ -13795,7 +13794,7 @@
         <v>668</v>
       </c>
       <c r="B952" s="2" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="953" spans="1:2" x14ac:dyDescent="0.2">
@@ -13803,15 +13802,15 @@
         <v>293</v>
       </c>
       <c r="B953" s="3" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A954" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B954" s="2" t="s">
         <v>1887</v>
-      </c>
-      <c r="B954" s="2" t="s">
-        <v>1888</v>
       </c>
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.2">
@@ -13819,31 +13818,31 @@
         <v>414</v>
       </c>
       <c r="B955" s="3" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A956" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B956" s="2" t="s">
         <v>1890</v>
-      </c>
-      <c r="B956" s="2" t="s">
-        <v>1891</v>
       </c>
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A957" s="3" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B957" s="3" t="s">
         <v>1892</v>
-      </c>
-      <c r="B957" s="3" t="s">
-        <v>1893</v>
       </c>
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A958" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B958" s="2" t="s">
         <v>1894</v>
-      </c>
-      <c r="B958" s="2" t="s">
-        <v>1895</v>
       </c>
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.2">
@@ -13851,55 +13850,55 @@
         <v>312</v>
       </c>
       <c r="B959" s="3" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A960" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B960" s="2" t="s">
         <v>1897</v>
-      </c>
-      <c r="B960" s="2" t="s">
-        <v>1898</v>
       </c>
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A961" s="3" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B961" s="3" t="s">
         <v>1899</v>
-      </c>
-      <c r="B961" s="3" t="s">
-        <v>1900</v>
       </c>
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A962" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B962" s="2" t="s">
         <v>1901</v>
-      </c>
-      <c r="B962" s="2" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A963" s="3" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B963" s="3" t="s">
         <v>1903</v>
-      </c>
-      <c r="B963" s="3" t="s">
-        <v>1904</v>
       </c>
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A964" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B964" s="2" t="s">
         <v>1905</v>
-      </c>
-      <c r="B964" s="2" t="s">
-        <v>1906</v>
       </c>
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A965" s="3" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B965" s="3" t="s">
         <v>1907</v>
-      </c>
-      <c r="B965" s="3" t="s">
-        <v>1908</v>
       </c>
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.2">
@@ -13907,7 +13906,7 @@
         <v>566</v>
       </c>
       <c r="B966" s="2" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.2">
@@ -13915,7 +13914,7 @@
         <v>599</v>
       </c>
       <c r="B967" s="3" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.2">
@@ -13923,7 +13922,7 @@
         <v>513</v>
       </c>
       <c r="B968" s="2" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.2">
@@ -13931,7 +13930,7 @@
         <v>667</v>
       </c>
       <c r="B969" s="3" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.2">
@@ -13939,7 +13938,7 @@
         <v>397</v>
       </c>
       <c r="B970" s="2" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.2">
@@ -13947,15 +13946,15 @@
         <v>655</v>
       </c>
       <c r="B971" s="3" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A972" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B972" s="2" t="s">
         <v>1915</v>
-      </c>
-      <c r="B972" s="2" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="973" spans="1:2" x14ac:dyDescent="0.2">
@@ -13963,12 +13962,12 @@
         <v>348</v>
       </c>
       <c r="B973" s="3" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="974" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A974" s="2" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B974" s="2" t="s">
         <v>565</v>
@@ -13979,39 +13978,39 @@
         <v>615</v>
       </c>
       <c r="B975" s="2" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A976" s="3" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B976" s="3" t="s">
         <v>1920</v>
-      </c>
-      <c r="B976" s="3" t="s">
-        <v>1921</v>
       </c>
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A977" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B977" s="2" t="s">
         <v>1922</v>
-      </c>
-      <c r="B977" s="2" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A978" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B978" s="3" t="s">
         <v>1924</v>
-      </c>
-      <c r="B978" s="3" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A979" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B979" s="2" t="s">
         <v>1926</v>
-      </c>
-      <c r="B979" s="2" t="s">
-        <v>1927</v>
       </c>
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.2">
@@ -14019,28 +14018,28 @@
         <v>652</v>
       </c>
       <c r="B980" s="3" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A981" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B981" s="2" t="s">
         <v>1929</v>
-      </c>
-      <c r="B981" s="2" t="s">
-        <v>1930</v>
       </c>
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A982" s="3" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B982" s="3" t="s">
         <v>1931</v>
-      </c>
-      <c r="B982" s="3" t="s">
-        <v>1932</v>
       </c>
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A983" s="2" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B983" s="2" t="s">
         <v>633</v>
@@ -14048,10 +14047,10 @@
     </row>
     <row r="984" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A984" s="3" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B984" s="3" t="s">
         <v>1934</v>
-      </c>
-      <c r="B984" s="3" t="s">
-        <v>1935</v>
       </c>
     </row>
     <row r="985" spans="1:2" x14ac:dyDescent="0.2">
@@ -14059,7 +14058,7 @@
         <v>479</v>
       </c>
       <c r="B985" s="2" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="986" spans="1:2" x14ac:dyDescent="0.2">
@@ -14067,7 +14066,7 @@
         <v>473</v>
       </c>
       <c r="B986" s="3" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
   </sheetData>

--- a/dutch-words.xlsx
+++ b/dutch-words.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="1937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="1993">
   <si>
     <t>Dutch</t>
   </si>
@@ -5831,6 +5831,174 @@
   </si>
   <si>
     <t>1. the (bed)sheet; 2. tablecloth</t>
+  </si>
+  <si>
+    <t>1. indeed, really (modal particle, e.g. "ik denk het wel" = I do think so); 2. as many as (before a number, e.g. "wel duizend")</t>
+  </si>
+  <si>
+    <t>1. it; 2. the (before neuter/het-nouns)</t>
+  </si>
+  <si>
+    <t>1. over, about; 2. [om kwart ~ zeven] at quarter past seven; 3. left, remaining</t>
+  </si>
+  <si>
+    <t>really; real</t>
+  </si>
+  <si>
+    <t>perhaps, maybe</t>
+  </si>
+  <si>
+    <t>1. very (adverb); 2. whole, entire (adjective)</t>
+  </si>
+  <si>
+    <t>the hate, hatred</t>
+  </si>
+  <si>
+    <t>to grab, take, catch, catch hold of</t>
+  </si>
+  <si>
+    <t>1. seven; 2. [om kwart voor ~] at quarter to seven</t>
+  </si>
+  <si>
+    <t>to hit, to touch, to make contact with</t>
+  </si>
+  <si>
+    <t>(you) tell, narrate; (he) tells, narrates</t>
+  </si>
+  <si>
+    <t>the rest, relaxation, peace and quiet</t>
+  </si>
+  <si>
+    <t>de zomer</t>
+  </si>
+  <si>
+    <t>the summer</t>
+  </si>
+  <si>
+    <t>de winter</t>
+  </si>
+  <si>
+    <t>the winter</t>
+  </si>
+  <si>
+    <t>de lente</t>
+  </si>
+  <si>
+    <t>the spring (season)</t>
+  </si>
+  <si>
+    <t>de herfst</t>
+  </si>
+  <si>
+    <t>the autumn, fall</t>
+  </si>
+  <si>
+    <t>het weer</t>
+  </si>
+  <si>
+    <t>the weather</t>
+  </si>
+  <si>
+    <t>de winkel</t>
+  </si>
+  <si>
+    <t>the shop, store</t>
+  </si>
+  <si>
+    <t>de keuken</t>
+  </si>
+  <si>
+    <t>the kitchen</t>
+  </si>
+  <si>
+    <t>negen</t>
+  </si>
+  <si>
+    <t>nine</t>
+  </si>
+  <si>
+    <t>elf</t>
+  </si>
+  <si>
+    <t>eleven</t>
+  </si>
+  <si>
+    <t>twaalf</t>
+  </si>
+  <si>
+    <t>twelve</t>
+  </si>
+  <si>
+    <t>maandag</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>dinsdag</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>woensdag</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>donderdag</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>vrijdag</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>zaterdag</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>zondag</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>rood</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>blauw</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>groen</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>geel</t>
+  </si>
+  <si>
+    <t>yellow</t>
+  </si>
+  <si>
+    <t>wit</t>
+  </si>
+  <si>
+    <t>white</t>
   </si>
 </sst>
 </file>
@@ -6174,7 +6342,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B986"/>
+  <dimension ref="A1:B1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.5" customWidth="1"/>
@@ -6306,7 +6474,7 @@
         <v>66</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>700</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -6370,7 +6538,7 @@
         <v>38</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>39</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -6439,10 +6607,10 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>1949</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>720</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -6722,7 +6890,7 @@
         <v>210</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>743</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
@@ -6898,7 +7066,7 @@
         <v>456</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>762</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
@@ -7370,7 +7538,7 @@
         <v>67</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>822</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
@@ -7498,7 +7666,7 @@
         <v>440</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>443</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
@@ -7815,10 +7983,10 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>67</v>
+        <v>1951</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>892</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
@@ -7919,10 +8087,10 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
-        <v>440</v>
+        <v>1953</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>908</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
@@ -9407,10 +9575,10 @@
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A404" s="3" t="s">
-        <v>456</v>
+        <v>1955</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>1137</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
@@ -10058,7 +10226,7 @@
         <v>671</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1238</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
@@ -10583,10 +10751,10 @@
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" s="3" t="s">
-        <v>671</v>
+        <v>1957</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1321</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
@@ -10719,10 +10887,10 @@
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" s="2" t="s">
-        <v>1343</v>
+        <v>1959</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1344</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.2">
@@ -10930,7 +11098,7 @@
         <v>1343</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>1380</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.2">
@@ -11119,10 +11287,10 @@
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A618" s="2" t="s">
-        <v>1302</v>
+        <v>1961</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1407</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.2">
@@ -11938,7 +12106,7 @@
         <v>244</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1545</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.2">
@@ -13146,7 +13314,7 @@
         <v>1763</v>
       </c>
       <c r="B871" s="3" t="s">
-        <v>1764</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.2">
@@ -13410,7 +13578,7 @@
         <v>1814</v>
       </c>
       <c r="B904" s="2" t="s">
-        <v>1815</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.2">
@@ -13490,7 +13658,7 @@
         <v>1829</v>
       </c>
       <c r="B914" s="2" t="s">
-        <v>1830</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.2">
@@ -14067,6 +14235,126 @@
       </c>
       <c r="B986" s="3" t="s">
         <v>1936</v>
+      </c>
+    </row>
+    <row r="987" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A987" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B987" s="2" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="988" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A988" s="3" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B988" s="3" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="989" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A989" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B989" s="2" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="990" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A990" s="3" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B990" s="3" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="991" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A991" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B991" s="2" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="992" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A992" s="3" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B992" s="3" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="993" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A993" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B993" s="2" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="994" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A994" s="3" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B994" s="3" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="995" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A995" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B995" s="2" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="996" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A996" s="3" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B996" s="3" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="997" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A997" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B997" s="2" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="998" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A998" s="3" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B998" s="3" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="999" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A999" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B999" s="2" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1000" s="3" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B1000" s="3" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1001" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B1001" s="2" t="s">
+        <v>1992</v>
       </c>
     </row>
   </sheetData>
